--- a/request_forms/033_cosmetics_product_development_request_form--request_forms.xlsx
+++ b/request_forms/033_cosmetics_product_development_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -853,8 +853,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -882,12 +882,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'skin_care',_'value':_'skin_care'}</t>
+          <t>skin_care</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Skin Care', 'value': 'skin_care'}</t>
+          <t>skin care</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'hair_care',_'value':_'hair_care'}</t>
+          <t>hair_care</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'Hair Care', 'value': 'hair_care'}</t>
+          <t>hair care</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'make_up',_'value':_'make_up'}</t>
+          <t>make_up</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'Make Up', 'value': 'make_up'}</t>
+          <t>make up</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'fragrance',_'value':_'fragrance'}</t>
+          <t>fragrance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'Fragrance', 'value': 'fragrance'}</t>
+          <t>fragrance</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'personal_care',_'value':_'personal_care'}</t>
+          <t>personal_care</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'Personal Care', 'value': 'personal_care'}</t>
+          <t>personal care</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'Other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'red',_'value':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'Red', 'value': 'red'}</t>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'blue',_'value':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'Blue', 'value': 'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'black',_'value':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'Black', 'value': 'black'}</t>
+          <t>black</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'green',_'value':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'Green', 'value': 'green'}</t>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'small',_'value':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'Small', 'value': 'small'}</t>
+          <t>small</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_26,_'name':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 26, 'name': 'Medium', 'value': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_27,_'name':_'large',_'value':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 27, 'name': 'Large', 'value': 'large'}</t>
+          <t>large</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_28,_'name':_'extra_large',_'value':_'extra_large'}</t>
+          <t>extra_large</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 28, 'name': 'Extra Large', 'value': 'extra_large'}</t>
+          <t>extra large</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_29,_'name':_'tube',_'value':_'tube'}</t>
+          <t>tube</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 29, 'name': 'Tube', 'value': 'tube'}</t>
+          <t>tube</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'bottle',_'value':_'bottle'}</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'Bottle', 'value': 'bottle'}</t>
+          <t>bottle</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_31,_'name':_'jar',_'value':_'jar'}</t>
+          <t>jar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 31, 'name': 'Jar', 'value': 'jar'}</t>
+          <t>jar</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'bag',_'value':_'bag'}</t>
+          <t>bag</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': 'Bag', 'value': 'bag'}</t>
+          <t>bag</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_33,_'name':_'box',_'value':_'box'}</t>
+          <t>box</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 33, 'name': 'Box', 'value': 'box'}</t>
+          <t>box</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_34,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 34, 'name': 'Other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
